--- a/installation/1403-11-01/windows10/components.xlsx
+++ b/installation/1403-11-01/windows10/components.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -95,7 +95,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -403,29 +403,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" customWidth="1"/>
-    <col min="2" max="2" width="93.42578125" customWidth="1"/>
-    <col min="3" max="3" width="53.28515625" customWidth="1"/>
+    <col min="1" max="1" width="41.25" customWidth="1"/>
+    <col min="2" max="2" width="93.375" customWidth="1"/>
+    <col min="3" max="3" width="53.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -436,7 +436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -444,7 +444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -452,7 +452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -463,17 +463,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -481,7 +481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -489,7 +489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
